--- a/Pruebas calificadas/COLEGIO AGUDELO RESTREPO-501_Ajustado_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO AGUDELO RESTREPO-501_Ajustado_CALIFICADO.xlsx
@@ -807,11 +807,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="inlineStr"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>111001801314</t>
@@ -1060,11 +1056,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t>111001801314</t>
@@ -1313,11 +1305,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>111001801314</t>
@@ -1566,11 +1554,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>111001801314</t>
@@ -1819,11 +1803,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
           <t>111001801314</t>
@@ -2072,11 +2052,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
           <t>111001801314</t>
@@ -2325,11 +2301,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
           <t>111001801314</t>
@@ -2574,11 +2546,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>111001801314</t>
@@ -2827,11 +2795,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>111001801314</t>
@@ -3080,11 +3044,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
           <t>111001801314</t>
@@ -3333,11 +3293,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
           <t>111001801314</t>
@@ -3574,11 +3530,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="2" t="inlineStr">
         <is>
           <t>111001801314</t>
@@ -3827,11 +3779,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A14" s="2" t="inlineStr"/>
       <c r="B14" s="2" t="inlineStr">
         <is>
           <t>111001801314</t>
@@ -4080,11 +4028,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A15" s="2" t="inlineStr"/>
       <c r="B15" s="2" t="inlineStr">
         <is>
           <t>111001801314</t>
@@ -4333,11 +4277,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A16" s="2" t="inlineStr"/>
       <c r="B16" s="2" t="inlineStr">
         <is>
           <t>111001801314</t>
@@ -4586,11 +4526,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
           <t>111001801314</t>
@@ -4839,11 +4775,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A18" s="2" t="inlineStr"/>
       <c r="B18" s="2" t="inlineStr">
         <is>
           <t>111001801314</t>
@@ -5092,11 +5024,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="inlineStr"/>
       <c r="B19" s="2" t="inlineStr">
         <is>
           <t>111001801314</t>
@@ -5345,11 +5273,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="inlineStr"/>
       <c r="B20" s="2" t="inlineStr">
         <is>
           <t>111001801314</t>
@@ -5598,11 +5522,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
           <t>111001801314</t>
@@ -5851,11 +5771,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A22" s="2" t="inlineStr"/>
       <c r="B22" s="2" t="inlineStr">
         <is>
           <t>111001801314</t>
@@ -6104,11 +6020,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="inlineStr"/>
       <c r="B23" s="2" t="inlineStr">
         <is>
           <t>111001801314</t>
@@ -6357,11 +6269,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="2" t="inlineStr">
         <is>
           <t>111001801314</t>
@@ -6610,11 +6518,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A25" s="2" t="inlineStr"/>
       <c r="B25" s="2" t="inlineStr">
         <is>
           <t>111001801314</t>
@@ -6863,11 +6767,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
           <t>111001801314</t>
@@ -7112,11 +7012,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
           <t>111001801314</t>
@@ -7365,11 +7261,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A28" s="2" t="inlineStr"/>
       <c r="B28" s="2" t="inlineStr">
         <is>
           <t>111001801314</t>
@@ -7618,11 +7510,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="inlineStr"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
           <t>111001801314</t>
@@ -7867,11 +7755,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A30" s="2" t="inlineStr"/>
       <c r="B30" s="2" t="inlineStr">
         <is>
           <t>111001801314</t>
@@ -8120,11 +8004,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
           <t>111001801314</t>
@@ -8373,11 +8253,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="inlineStr"/>
       <c r="B32" s="2" t="inlineStr">
         <is>
           <t>111001801314</t>
@@ -8626,11 +8502,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A33" s="2" t="inlineStr"/>
       <c r="B33" s="2" t="inlineStr">
         <is>
           <t>111001801314</t>
@@ -8875,11 +8747,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A34" s="2" t="inlineStr"/>
       <c r="B34" s="2" t="inlineStr">
         <is>
           <t>111001801314</t>
@@ -9128,11 +8996,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A35" s="2" t="inlineStr"/>
       <c r="B35" s="2" t="inlineStr">
         <is>
           <t>111001801314</t>
@@ -9381,11 +9245,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="inlineStr"/>
       <c r="B36" s="2" t="inlineStr">
         <is>
           <t>111001801314</t>
@@ -9634,11 +9494,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A37" s="2" t="inlineStr"/>
       <c r="B37" s="2" t="inlineStr">
         <is>
           <t>111001801314</t>
@@ -9883,11 +9739,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A38" s="2" t="inlineStr"/>
       <c r="B38" s="2" t="inlineStr">
         <is>
           <t>111001801314</t>
@@ -10136,11 +9988,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="2" t="inlineStr">
         <is>
           <t>111001801314</t>
@@ -10389,11 +10237,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A40" s="2" t="inlineStr"/>
       <c r="B40" s="2" t="inlineStr">
         <is>
           <t>111001801314</t>
@@ -10642,11 +10486,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A41" s="2" t="inlineStr"/>
       <c r="B41" s="2" t="inlineStr">
         <is>
           <t>111001801314</t>
@@ -10895,11 +10735,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A42" s="2" t="inlineStr"/>
       <c r="B42" s="2" t="inlineStr">
         <is>
           <t>111001801314</t>
@@ -11144,11 +10980,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A43" s="2" t="inlineStr"/>
       <c r="B43" s="2" t="inlineStr">
         <is>
           <t>111001801314</t>
@@ -11393,11 +11225,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A44" s="2" t="inlineStr"/>
       <c r="B44" s="2" t="inlineStr">
         <is>
           <t>111001801314</t>
@@ -11642,11 +11470,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A45" s="2" t="inlineStr"/>
       <c r="B45" s="2" t="inlineStr">
         <is>
           <t>111001801314</t>
@@ -11895,11 +11719,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A46" s="2" t="inlineStr"/>
       <c r="B46" s="2" t="inlineStr">
         <is>
           <t>111001801314</t>
@@ -12136,11 +11956,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A47" s="2" t="inlineStr"/>
       <c r="B47" s="2" t="inlineStr">
         <is>
           <t>111001801314</t>
@@ -12389,11 +12205,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A48" s="2" t="inlineStr"/>
       <c r="B48" s="2" t="inlineStr">
         <is>
           <t>111001801314</t>
@@ -12634,11 +12446,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A49" s="2" t="inlineStr"/>
       <c r="B49" s="2" t="inlineStr">
         <is>
           <t>111001801314</t>
@@ -12887,11 +12695,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A50" s="2" t="inlineStr"/>
       <c r="B50" s="2" t="inlineStr">
         <is>
           <t>111001801314</t>
@@ -13140,11 +12944,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A51" s="2" t="inlineStr"/>
       <c r="B51" s="2" t="inlineStr">
         <is>
           <t>111001801314</t>
@@ -13393,11 +13193,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A52" s="2" t="inlineStr"/>
       <c r="B52" s="2" t="inlineStr">
         <is>
           <t>111001801314</t>
@@ -13646,11 +13442,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A53" s="2" t="inlineStr"/>
       <c r="B53" s="2" t="inlineStr">
         <is>
           <t>111001801314</t>
@@ -13891,11 +13683,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A54" s="2" t="inlineStr"/>
       <c r="B54" s="2" t="inlineStr">
         <is>
           <t>111001801314</t>
@@ -14144,11 +13932,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A55" s="2" t="inlineStr"/>
       <c r="B55" s="2" t="inlineStr">
         <is>
           <t>111001801314</t>
@@ -14397,11 +14181,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A56" s="2" t="inlineStr"/>
       <c r="B56" s="2" t="inlineStr">
         <is>
           <t>111001801314</t>
@@ -14650,11 +14430,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A57" s="2" t="inlineStr"/>
       <c r="B57" s="2" t="inlineStr">
         <is>
           <t>111001801314</t>
@@ -14903,11 +14679,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A58" s="2" t="inlineStr"/>
       <c r="B58" s="2" t="inlineStr">
         <is>
           <t>111001801314</t>
@@ -15152,11 +14924,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A59" s="2" t="inlineStr"/>
       <c r="B59" s="2" t="inlineStr">
         <is>
           <t>111001801314</t>
@@ -15393,11 +15161,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A60" s="2" t="inlineStr"/>
       <c r="B60" s="2" t="inlineStr">
         <is>
           <t>111001801314</t>
@@ -15646,11 +15410,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A61" s="2" t="inlineStr"/>
       <c r="B61" s="2" t="inlineStr">
         <is>
           <t>111001801314</t>
@@ -15875,11 +15635,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A62" s="2" t="inlineStr"/>
       <c r="B62" s="2" t="inlineStr">
         <is>
           <t>111001801314</t>
@@ -16120,11 +15876,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A63" s="2" t="inlineStr"/>
       <c r="B63" s="2" t="inlineStr">
         <is>
           <t>111001801314</t>
@@ -16373,11 +16125,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A64" s="2" t="inlineStr"/>
       <c r="B64" s="2" t="inlineStr">
         <is>
           <t>111001801314</t>
@@ -16626,11 +16374,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A65" s="2" t="inlineStr"/>
       <c r="B65" s="2" t="inlineStr">
         <is>
           <t>111001801314</t>
@@ -16879,11 +16623,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A66" s="2" t="inlineStr"/>
       <c r="B66" s="2" t="inlineStr">
         <is>
           <t>111001801314</t>
@@ -17132,11 +16872,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A67" s="2" t="inlineStr"/>
       <c r="B67" s="2" t="inlineStr">
         <is>
           <t>111001801314</t>
@@ -17385,11 +17121,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A68" s="2" t="inlineStr"/>
       <c r="B68" s="2" t="inlineStr">
         <is>
           <t>111001801314</t>
@@ -17630,11 +17362,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A69" s="2" t="inlineStr"/>
       <c r="B69" s="2" t="inlineStr">
         <is>
           <t>111001801314</t>
@@ -17883,11 +17611,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A70" s="2" t="inlineStr"/>
       <c r="B70" s="2" t="inlineStr">
         <is>
           <t>111001801314</t>
@@ -18132,11 +17856,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A71" s="2" t="inlineStr"/>
       <c r="B71" s="2" t="inlineStr">
         <is>
           <t>111001801314</t>
@@ -18385,11 +18105,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A72" s="2" t="inlineStr"/>
       <c r="B72" s="2" t="inlineStr">
         <is>
           <t>111001801314</t>
@@ -18638,11 +18354,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A73" s="2" t="inlineStr"/>
       <c r="B73" s="2" t="inlineStr">
         <is>
           <t>111001801314</t>
@@ -18891,11 +18603,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A74" s="2" t="inlineStr"/>
       <c r="B74" s="2" t="inlineStr">
         <is>
           <t>111001801314</t>
@@ -19144,11 +18852,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A75" s="2" t="inlineStr"/>
       <c r="B75" s="2" t="inlineStr">
         <is>
           <t>111001801314</t>
@@ -19385,11 +19089,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A76" s="2" t="inlineStr"/>
       <c r="B76" s="2" t="inlineStr">
         <is>
           <t>111001801314</t>
@@ -19638,11 +19338,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A77" s="2" t="inlineStr"/>
       <c r="B77" s="2" t="inlineStr">
         <is>
           <t>111001801314</t>
@@ -19887,11 +19583,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A78" s="2" t="inlineStr"/>
       <c r="B78" s="2" t="inlineStr">
         <is>
           <t>111001801314</t>
@@ -20140,11 +19832,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A79" s="2" t="inlineStr"/>
       <c r="B79" s="2" t="inlineStr">
         <is>
           <t>111001801314</t>
@@ -20393,11 +20081,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A80" s="2" t="inlineStr"/>
       <c r="B80" s="2" t="inlineStr">
         <is>
           <t>111001801314</t>
@@ -20646,11 +20330,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A81" s="2" t="inlineStr"/>
       <c r="B81" s="2" t="inlineStr">
         <is>
           <t>111001801314</t>
